--- a/Novotel-February-2026.xlsx
+++ b/Novotel-February-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2023031\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834D72EA-451D-4C73-8B57-89CA029BA952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2764883F-7A96-434B-A750-4D6D932860BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E82819E8-EFF0-4774-BA8F-CEEEEB2C50F6}"/>
   </bookViews>
@@ -657,7 +657,7 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G9" ca="1" si="0">TODAY()-RANDBETWEEN(365,365*5)</f>
-        <v>45747</v>
+        <v>44651</v>
       </c>
       <c r="H2">
         <v>77622</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -738,7 +738,7 @@
       </c>
       <c r="G3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44971</v>
+        <v>45347</v>
       </c>
       <c r="H3">
         <v>74250</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44400</v>
+        <v>45639</v>
       </c>
       <c r="H4">
         <v>91399</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="G5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45439</v>
+        <v>45283</v>
       </c>
       <c r="H5">
         <v>100198</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="G6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44847</v>
+        <v>44797</v>
       </c>
       <c r="H6">
         <v>93482</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44783</v>
+        <v>45642</v>
       </c>
       <c r="H7">
         <v>96107</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45500</v>
+        <v>45064</v>
       </c>
       <c r="H8">
         <v>86027</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44810</v>
+        <v>44804</v>
       </c>
       <c r="H9">
         <v>99500</v>

--- a/Novotel-February-2026.xlsx
+++ b/Novotel-February-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2023031\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2764883F-7A96-434B-A750-4D6D932860BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C8D003-EF74-4A2F-BEC6-EC30A97D7B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E82819E8-EFF0-4774-BA8F-CEEEEB2C50F6}"/>
   </bookViews>
@@ -656,8 +656,8 @@
         <v>14</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G9" ca="1" si="0">TODAY()-RANDBETWEEN(365,365*5)</f>
-        <v>44651</v>
+        <f ca="1">TODAY()-RANDBETWEEN(365,365*2)</f>
+        <v>45588</v>
       </c>
       <c r="H2">
         <v>77622</v>
@@ -737,8 +737,8 @@
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45347</v>
+        <f t="shared" ref="G3:G9" ca="1" si="0">TODAY()-RANDBETWEEN(365,365*2)</f>
+        <v>45541</v>
       </c>
       <c r="H3">
         <v>74250</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45639</v>
+        <v>45457</v>
       </c>
       <c r="H4">
         <v>91399</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="G5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45283</v>
+        <v>45698</v>
       </c>
       <c r="H5">
         <v>100198</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="G6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44797</v>
+        <v>45563</v>
       </c>
       <c r="H6">
         <v>93482</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45642</v>
+        <v>45779</v>
       </c>
       <c r="H7">
         <v>96107</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45064</v>
+        <v>45437</v>
       </c>
       <c r="H8">
         <v>86027</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44804</v>
+        <v>45709</v>
       </c>
       <c r="H9">
         <v>99500</v>

--- a/Novotel-February-2026.xlsx
+++ b/Novotel-February-2026.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="G2" s="1">
         <f ca="1">TODAY()-RANDBETWEEN(365,365*2)</f>
-        <v>45588</v>
+        <v>45672</v>
       </c>
       <c r="H2">
         <v>77622</v>
@@ -738,7 +738,7 @@
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G9" ca="1" si="0">TODAY()-RANDBETWEEN(365,365*2)</f>
-        <v>45541</v>
+        <v>45529</v>
       </c>
       <c r="H3">
         <v>74250</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45457</v>
+        <v>45685</v>
       </c>
       <c r="H4">
         <v>91399</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="G5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45698</v>
+        <v>45660</v>
       </c>
       <c r="H5">
         <v>100198</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="G6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45563</v>
+        <v>45590</v>
       </c>
       <c r="H6">
         <v>93482</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45553</v>
       </c>
       <c r="H7">
         <v>96107</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45437</v>
+        <v>45533</v>
       </c>
       <c r="H8">
         <v>86027</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="H9">
         <v>99500</v>

--- a/Novotel-February-2026.xlsx
+++ b/Novotel-February-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2023031\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C8D003-EF74-4A2F-BEC6-EC30A97D7B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38506660-FED6-4C50-A5B9-CAEC34A7B5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E82819E8-EFF0-4774-BA8F-CEEEEB2C50F6}"/>
   </bookViews>
@@ -656,8 +656,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="1">
-        <f ca="1">TODAY()-RANDBETWEEN(365,365*2)</f>
-        <v>45672</v>
+        <v>45490</v>
       </c>
       <c r="H2">
         <v>77622</v>
@@ -737,8 +736,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G9" ca="1" si="0">TODAY()-RANDBETWEEN(365,365*2)</f>
-        <v>45529</v>
+        <v>45222</v>
       </c>
       <c r="H3">
         <v>74250</v>
@@ -818,8 +816,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45685</v>
+        <v>45805</v>
       </c>
       <c r="H4">
         <v>91399</v>
@@ -899,8 +896,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45660</v>
+        <v>45052</v>
       </c>
       <c r="H5">
         <v>100198</v>
@@ -980,8 +976,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45590</v>
+        <v>44424</v>
       </c>
       <c r="H6">
         <v>93482</v>
@@ -1061,8 +1056,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45553</v>
+        <v>45274</v>
       </c>
       <c r="H7">
         <v>96107</v>
@@ -1142,8 +1136,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45533</v>
+        <v>45778</v>
       </c>
       <c r="H8">
         <v>86027</v>
@@ -1223,8 +1216,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45710</v>
+        <v>44888</v>
       </c>
       <c r="H9">
         <v>99500</v>

--- a/Novotel-February-2026.xlsx
+++ b/Novotel-February-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Novotel</t>
   </si>
   <si>
@@ -124,7 +127,7 @@
     <t>HR38AD1224</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>21/09/2021</t>
@@ -501,10 +504,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,28 +586,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>194</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>77622</v>
@@ -664,27 +670,27 @@
         <v>40.59</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>195</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3">
         <v>74250</v>
@@ -744,27 +750,27 @@
         <v>51.77</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>196</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4">
         <v>91399</v>
@@ -824,27 +830,27 @@
         <v>51.61</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>100198</v>
@@ -904,24 +910,24 @@
         <v>34.32</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2">
         <v>44106</v>
@@ -984,24 +990,24 @@
         <v>49.58</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="2">
         <v>44106</v>
@@ -1064,27 +1070,27 @@
         <v>49.96</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8">
         <v>86027</v>
@@ -1144,27 +1150,27 @@
         <v>45.17</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>201</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9">
         <v>99500</v>
